--- a/signals_2025-08.xlsx
+++ b/signals_2025-08.xlsx
@@ -2343,12 +2343,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SL Oldu</t>
+          <t>TP Oldu</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2025-08-11 21:51:15</t>
+          <t>2025-11-30 01:33:37</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SL Oldu</t>
+          <t>TP Oldu</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2025-08-14 08:19:34</t>
+          <t>2025-11-30 01:33:37</t>
         </is>
       </c>
     </row>
